--- a/data/trans_orig/IP1014-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Habitat-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149858</t>
+          <t>149677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288653</t>
+          <t>288598</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191945</t>
+          <t>191466</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207319</t>
+          <t>207365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>401852</t>
+          <t>401342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406663</t>
+          <t>406664</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146438</t>
+          <t>146408</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284253</t>
+          <t>284262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>204300</t>
+          <t>204325</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413623</t>
+          <t>413203</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>678079</t>
+          <t>677995</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715780</t>
+          <t>714541</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>721379</t>
+          <t>721349</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395022</t>
+          <t>1395565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402338</t>
+          <t>1402370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131573</t>
+          <t>131208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149646</t>
+          <t>148997</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>283160</t>
+          <t>284327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217649</t>
+          <t>218125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>422630</t>
+          <t>423506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152583</t>
+          <t>152802</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162687</t>
+          <t>162671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317179</t>
+          <t>316954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200720</t>
+          <t>200740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>206460</t>
+          <t>206459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411808</t>
+          <t>411248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416761</t>
+          <t>416742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9086</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>11708</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>702001</t>
+          <t>700603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739056</t>
+          <t>738888</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>746133</t>
+          <t>746185</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443713</t>
+          <t>1443362</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1452308</t>
+          <t>1451880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218481</t>
+          <t>219013</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>223745</t>
+          <t>223743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>426213</t>
+          <t>426511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430989</t>
+          <t>430990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6033,47 +6033,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>617</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5357</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>739487</t>
+          <t>739598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744227</t>
+          <t>744225</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443872</t>
+          <t>1443342</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1448600</t>
+          <t>1448598</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/IP1014-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1014-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4269</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152404</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>148808</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152404</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>149677</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>428</t>
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288598</t>
+          <t>288098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4845</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3697</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1384</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4777</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>210758</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>207297</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>194521</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191466</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191664</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>210758</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>207365</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,75%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>631</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>401342</t>
+          <t>401576</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406664</t>
+          <t>406663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,92 +1408,92 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3249</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149015</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>146453</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149015</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>146408</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,83%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>460</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284262</t>
+          <t>284261</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3506</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3499</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3508</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3936</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207124</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>204318</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207124</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>204325</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,32%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>579</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413203</t>
+          <t>413631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7549</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3590</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8159</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8156</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>719301</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>715151</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>721353</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>680379</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>677995</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>677431</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,91%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>719301</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>714541</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>721349</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,87%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2098</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1395565</t>
+          <t>1395462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402370</t>
+          <t>1401802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2674,87 +2674,87 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3509</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>896</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5183</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5342</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1583</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>152411</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>149589</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135495</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>131208</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>131049</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>152411</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>148997</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>392</t>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284327</t>
+          <t>284330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1245</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3852</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4633</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3870</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>220732</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>218112</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>220732</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>218125</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>636</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423506</t>
+          <t>422743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3360,102 +3360,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2181</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1097</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3314</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3757</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1097</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3870</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165331</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162868</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,61%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154396</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>152802</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>152658</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,59%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165331</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>162671</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>494</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316954</t>
+          <t>317067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,92 +3698,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5685</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>2106</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6342</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>624</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204976</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201397</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>206459</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204976</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>200740</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>206459</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>553</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411248</t>
+          <t>411630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416742</t>
+          <t>416758</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9563</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6325</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5560</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9254</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>2671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>743451</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>738579</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>746107</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,72%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705589</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>700603</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>701368</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1059</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>743451</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>738888</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>746185</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2075</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443362</t>
+          <t>1444532</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1451880</t>
+          <t>1452399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4729,47 +4729,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,92 +4959,92 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5899</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5346</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>222364</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>218460</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>223740</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>222364</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>219013</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>223743</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>663</t>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>426511</t>
+          <t>426217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>430990</t>
+          <t>430987</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5415,47 +5415,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,84 +5988,84 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5701</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1995</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5246</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1995</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
           <t>617</t>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742849</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>739143</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744250</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742849</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>739598</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744225</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2123</t>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1443342</t>
+          <t>1443163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
